--- a/Employee_Reports_wi48/Peter Nganga Kamau Q0593.xlsx
+++ b/Employee_Reports_wi48/Peter Nganga Kamau Q0593.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1189,9 +1189,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>06-Jun-2026</t>
@@ -1203,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1301,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1350,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1399,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1522,11 +1534,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2019,7 +2031,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2048,7 +2060,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2077,7 +2089,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2106,7 +2118,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2147,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
